--- a/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -567,6 +567,10 @@
 priorrenewed order</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/requestgroup-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
+  </si>
+  <si>
     <t>Request(s) replaced by this request</t>
   </si>
   <si>
@@ -705,7 +709,7 @@
     <t>RequestGroup.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/group-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -724,7 +728,7 @@
     <t>RequestGroup.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -762,7 +766,7 @@
     <t>RequestGroup.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -796,7 +800,7 @@
     <t>RequestGroup.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1083,7 +1087,7 @@
     <t>RequestGroup.action.participant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Device) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/device-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -3254,19 +3258,19 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3330,7 +3334,7 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
@@ -3341,14 +3345,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3370,16 +3374,16 @@
         <v>151</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3428,7 +3432,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3443,7 +3447,7 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
@@ -3454,10 +3458,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3483,10 +3487,10 @@
         <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3513,13 +3517,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3537,7 +3541,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>85</v>
@@ -3552,10 +3556,10 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3563,14 +3567,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3592,14 +3596,14 @@
         <v>105</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3624,13 +3628,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3648,7 +3652,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3663,10 +3667,10 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3674,10 +3678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3703,10 +3707,10 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3714,7 +3718,7 @@
         <v>20</v>
       </c>
       <c r="Q20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="R20" t="s" s="2">
         <v>20</v>
@@ -3735,13 +3739,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3759,7 +3763,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3774,10 +3778,10 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -3785,10 +3789,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3811,16 +3815,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3870,7 +3874,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3885,10 +3889,10 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
@@ -3896,10 +3900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3922,13 +3926,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3979,7 +3983,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3994,10 +3998,10 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -4005,10 +4009,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4031,13 +4035,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4088,7 +4092,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4103,10 +4107,10 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4114,10 +4118,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4140,13 +4144,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4197,7 +4201,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4212,10 +4216,10 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4223,10 +4227,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4249,13 +4253,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4306,7 +4310,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4321,10 +4325,10 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4332,10 +4336,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4358,13 +4362,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4415,7 +4419,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4430,10 +4434,10 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4441,10 +4445,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4467,13 +4471,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4524,7 +4528,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4539,10 +4543,10 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4550,10 +4554,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4576,13 +4580,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4633,7 +4637,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4648,7 +4652,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
@@ -4659,10 +4663,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4685,13 +4689,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4742,7 +4746,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4754,7 +4758,7 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4768,10 +4772,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4794,13 +4798,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4851,7 +4855,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4872,15 +4876,15 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4906,10 +4910,10 @@
         <v>130</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>147</v>
@@ -4962,7 +4966,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4983,19 +4987,19 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5017,10 +5021,10 @@
         <v>130</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>147</v>
@@ -5075,7 +5079,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5101,10 +5105,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5127,13 +5131,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5184,7 +5188,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5210,10 +5214,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5236,13 +5240,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5293,7 +5297,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5319,10 +5323,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5345,13 +5349,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5402,7 +5406,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5428,10 +5432,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5454,13 +5458,13 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5511,7 +5515,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5537,10 +5541,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5566,10 +5570,10 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5596,13 +5600,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5620,7 +5624,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5635,7 +5639,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -5646,10 +5650,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5672,13 +5676,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5729,7 +5733,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5744,7 +5748,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -5755,10 +5759,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5781,13 +5785,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5838,7 +5842,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5853,7 +5857,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -5864,10 +5868,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5890,16 +5894,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5949,7 +5953,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5975,10 +5979,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6001,13 +6005,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6058,7 +6062,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6079,15 +6083,15 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6113,10 +6117,10 @@
         <v>130</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>147</v>
@@ -6169,7 +6173,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6190,19 +6194,19 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6224,10 +6228,10 @@
         <v>130</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>147</v>
@@ -6282,7 +6286,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6308,10 +6312,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6337,13 +6341,13 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6369,13 +6373,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6393,7 +6397,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6419,10 +6423,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6445,16 +6449,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6504,7 +6508,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6556,13 +6560,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6613,7 +6617,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6639,10 +6643,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6665,13 +6669,13 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6722,7 +6726,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6743,15 +6747,15 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6777,10 +6781,10 @@
         <v>130</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>147</v>
@@ -6833,7 +6837,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6854,19 +6858,19 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6888,10 +6892,10 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>147</v>
@@ -6946,7 +6950,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6972,10 +6976,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7001,10 +7005,10 @@
         <v>87</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7055,7 +7059,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>85</v>
@@ -7081,10 +7085,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7110,10 +7114,10 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7140,13 +7144,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7164,7 +7168,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>85</v>
@@ -7190,10 +7194,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7216,13 +7220,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7273,7 +7277,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7299,10 +7303,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7325,13 +7329,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7382,7 +7386,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7397,7 +7401,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>20</v>
@@ -7408,10 +7412,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7434,13 +7438,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7491,7 +7495,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7506,10 +7510,10 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -7517,10 +7521,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7543,13 +7547,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7576,13 +7580,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -7600,7 +7604,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7626,10 +7630,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7655,10 +7659,10 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7685,13 +7689,13 @@
         <v>20</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>20</v>
@@ -7709,7 +7713,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7735,10 +7739,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7764,10 +7768,10 @@
         <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7794,13 +7798,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -7818,7 +7822,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7844,10 +7848,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7873,10 +7877,10 @@
         <v>105</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7903,13 +7907,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -7927,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7953,10 +7957,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7982,10 +7986,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8012,13 +8016,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8036,7 +8040,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8062,10 +8066,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8091,10 +8095,10 @@
         <v>105</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8121,13 +8125,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8145,7 +8149,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8171,10 +8175,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8200,13 +8204,13 @@
         <v>168</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8256,7 +8260,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8265,7 +8269,7 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>97</v>
@@ -8282,10 +8286,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8311,10 +8315,10 @@
         <v>78</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8365,7 +8369,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8374,7 +8378,7 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>97</v>

--- a/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-requestgroup-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
